--- a/data/invalid_jobs.xlsx
+++ b/data/invalid_jobs.xlsx
@@ -1,73 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>url</t>
-  </si>
-  <si>
-    <t>reason</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <name val="Calibri"/>
       <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -114,74 +156,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -233,7 +215,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -242,13 +224,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -282,17 +264,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -347,68 +318,93 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="26" width="13.571428571428571" customWidth="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="53.33000183105469" customWidth="1" min="2" max="2"/>
+    <col width="24.44000053405762" customWidth="1" min="3" max="3"/>
+    <col width="13.5714282989502" customWidth="1" min="4" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>job_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa3b8415c11cce360365dea</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'This job has closed.'</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>url:f287e6d98517e5449d88</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa39ad5959a10d7230d2b10</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>U.S. citizenship explicitly required: page shows 'U.S. Citizen Only' and 'applicant must be a U.S. citizen, lawful permanent resident of the U.S...'</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>url:f021dbdd02bbe13a2450</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a427c4d6a9c2774b3fa628c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Job explicitly requires U.S. citizenship: tags state 'U.S. Citizen Only' and 'Security Clearance Required', and requirements state 'Active US Security clearance, or eligibility and willingness to obtain a US Security clearance'.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>url:8817e76c8bbee3ba318e</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/data/invalid_jobs.xlsx
+++ b/data/invalid_jobs.xlsx
@@ -6,16 +6,23 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -28,20 +35,27 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -156,14 +170,74 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
-        <a:ea typeface="Calibri Light"/>
-        <a:cs typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -215,7 +289,7 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -224,13 +298,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -264,6 +338,17 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -318,6 +403,47 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -327,13 +453,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="53.33000183105469" customWidth="1" min="2" max="2"/>
-    <col width="24.44000053405762" customWidth="1" min="3" max="3"/>
-    <col width="13.5714282989502" customWidth="1" min="4" max="24"/>
+    <col width="42.14285714285715" customWidth="1" min="1" max="1"/>
+    <col width="63.14285714285715" customWidth="1" min="2" max="2"/>
+    <col width="24.42857142857143" customWidth="1" min="3" max="3"/>
+    <col width="13.57142857142857" customWidth="1" min="4" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -404,7 +530,836 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa5957b930bff471a29f388</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>No Gmail confirmation for Zetheta Software Engineer. Supplied URL page shows Amazon SDE Early Career 10529830 submitted, which does not match target, so submission cannot be confirmed.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>url:2bc473229b9b8de58cdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6be65057120971bf3a974a</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Requires U.S. person status under export regulations: 'applicant must be a (i) U.S. citizen or national, (ii) U.S. lawful, permanent resident, (iii) Refugee, or (iv) Asylee, or be eligible to obtain the required authorizations'</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>url:54888fc9cf4ff758f5ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a92f2c0d18f75674827c8b9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>U.S. citizenship explicitly required: 'U.S. Citizenship Required: Yes' and 'U.S. Citizen Only' with 'Security Clearance Required'.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>url:d9c3d53b59aba93dd6a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/growth-engineer-at-velcor-ai-4464717896?position=48&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=02%2BB3N9Js0QruSu2FChgyA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Job is no longer accepting applications - page states 'Not currently accepting applications'.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>linkedin:4464717896</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-at-invoke-4466723011?position=45&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=4GEyYXB0shA3LtXusCaXww%3D%3D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>U.S. citizenship explicitly required: 'As this role supports public sector clients, U.S. citizenship is required.'</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>linkedin:4466723011</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/applied-ai-engineer-python-ai-at-remotehunter-4465422533?position=42&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=DANaeqW8mTSG2Demf0f4YQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'No longer accepting applications' - job is closed/no longer accepting applications.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>linkedin:4465422533</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/applied-ai-engineer-at-remotehunter-4465407692?position=39&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=3JucW8u4mFIKo70laovJug%3D%3D</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'No longer accepting applications' for Applied AI Engineer role.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>linkedin:4465407692</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-i-data-engineering-at-talenthop-4464725098?position=37&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=4qI2kTIjyHtWBwJAbV8XUA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Page explicitly shows 'No longer accepting applications' for this job.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>linkedin:4464725098</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/government-and-public-sector-service-delivery-center-ai-solution-developer-at-ey-4456255690?position=28&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=2zZ4bdla170DouruEUlRhQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Requires ability to obtain and maintain a secret clearance or higher: 'Must be able to obtain and maintain a secret clearance or higher'</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>linkedin:4456255690</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/artificial-intelligence-machine-learning-ai-ml-engineer-1-ts-sci-w-poly-at-peraton-4447160637?position=22&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=5wp1LgyjROnlmxTFRzD4Dg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Security clearance required: Title includes 'TS/SCI w/Poly' and description states 'An active TS/SCI with Poly is required.' Job in Laurel, MD is otherwise active.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>linkedin:4447160637</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/government-and-public-sector-service-delivery-center-ai-solution-developer-at-ey-4456274653?position=25&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=AS1%2BPX%2BZnm0GeMrIrKeh0Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Requires security clearance: 'Must be able to obtain and maintain a secret clearance or higher'</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>linkedin:4456274653</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-new-grad-at-yara-ai-4466734997?position=7&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=23lvmTpqCM%2F4ewHLtHqRrw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'No longer accepting applications' - job is closed/no longer accepting applications.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>linkedin:4466734997</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-applied-ai-%E2%80%94-new-grad-at-jobright-ai-4465423380?position=2&amp;pageNum=0&amp;refId=u8HajVcgeCXAd8%2BrAyuGYg%3D%3D&amp;trackingId=LdGuO4TPK%2F3mXsOSzApVSg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'No longer accepting applications'.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>linkedin:4465423380</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-applied-ai-%E2%80%94-new-grad-at-jobright-ai-4465701217/?refId=CVaHYM2dc%2FUClla2nuz%2BNg%3D%3D&amp;trackingId=OLKcpEROk2aEyI%2FH%2Fj6f1Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Page explicitly shows 'No longer accepting applications' for this job.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>linkedin:4465701217</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-ai-engineer-at-kpmg-us-4461343460?position=8&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=TmFaqnGd5vfEELubgUbcwg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Employer explicitly states OPT cannot be supported: 'no sponsorship is available for H-1B, L-1, TN, O-1, E-3, H-1B1, F-1, J-1, OPT, CPT or any other employment-based visa'</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>linkedin:4461343460</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-ai-engineer-at-kpmg-us-4461334809?position=6&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=%2FidaNKeYdMF9BvrvLRqIfw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Employer explicitly states OPT cannot be supported: 'KPMG LLP will not sponsor applicants for U.S. work visa status for this opportunity (no sponsorship is available for H-1B, L-1, TN, O-1, E-3, H-1B1, F-1, J-1, OPT, CPT or any other employment-based visa)'</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>linkedin:4461334809</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/junior-ai-software-engineer-at-dark-wolf-4467257232?position=3&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=Tac82xTqA2SCgQTvQK8c1Q%3D%3D</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Requires 'Must be a US Citizen holding an active TS/SCI security clearance with an active Full-Scope Polygraph' and 'US Citizenship with an active TS/SCI security clearance with Full-Scope Polygraph'</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>linkedin:4467257232</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-entry-level-at-jobright-ai-4466116399?position=1&amp;pageNum=0&amp;refId=KlUhDZviVKUkzqBmptZ1MQ%3D%3D&amp;trackingId=Jra%2FC5mViByEustbUJqOPA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>linkedin:4466116399</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-and-machine-learning-engineering-graduate-at-hewlett-packard-enterprise-4467038289?position=7&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=ay0y7FO300DSyUw81rf7GQ%3D%3D</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>linkedin:4467038289</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/applied-machine-learning-engineer-all-levels-at-allstate-4466113708?position=10&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=Yv2yC7mDD0lv1zOtl%2B1grA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>linkedin:4466113708</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/research-engineer-%E2%80%93-machine-learning-robotics-at-jumio-corporation-4434055122?position=9&amp;pageNum=0&amp;refId=AURhuN3PHp7W0ZQluz4k1Q%3D%3D&amp;trackingId=Wy%2FaAg9VyrZx%2Bw%2Bnfw0E1A%3D%3D</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>linkedin:4434055122</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa83eaf654b2a9424cfb84a</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>url:57b33d8c0f2a58757750</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa8b3b517ddad6a8a47ccb3</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Job explicitly states 'U.S. Citizen Only' and 'Security Clearance Required' with 'Candidate must have a TS/SCI'</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>url:d8c9954048046e961506</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9f74dca7ba386c5d675258</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Application was not submitted. Automatic recovery exhausted. {"decision": {"is_applied": false, "requires_login": false, "requires_human": false, "human_intervention_reason": "OTHER", "human_intervention_prompt": "Technical blocker on step 3 of 5 Application Questions: required transcript upload has no supplied file. Save and Continue blocked with validation error. Verified no submission occurred."}}</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>url:0bc74c71bf1819382974</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa7dfc1a77a53f5a15763b3</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>url:090dab0cb14cc060fbd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-applied-ai-%E2%80%94-new-grad-at-jobright-ai-4466580865?position=2&amp;pageNum=0&amp;refId=GT7CTRqsTUD1POoqrCpvtA%3D%3D&amp;trackingId=BTKaU9Vw31A9Kq02MkN6Uw%3D%3D</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>linkedin:4466580865</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-i-ai-agents-at-observe-ai-4467776863?position=7&amp;pageNum=0&amp;refId=OabEITA2YNRn6ahbARU6dg%3D%3D&amp;trackingId=2gfu%2FauaLJZGV%2F6nzFvN%2BA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Already applied - page shows 'Application submitted 4 hours ago' for Software Engineer I - AI Agents at Observe.AI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>linkedin:4467776863</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/associate-ai-software-engineer-at-internet-brands-4432304726?position=10&amp;pageNum=0&amp;refId=OabEITA2YNRn6ahbARU6dg%3D%3D&amp;trackingId=Zvsx4e%2F5rIC8xAPdr04%2Fow%3D%3D</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>linkedin:4432304726</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-at-qualcomm-4466513389?position=8&amp;pageNum=0&amp;refId=OabEITA2YNRn6ahbARU6dg%3D%3D&amp;trackingId=nixZXQtxab7tCciktJt6dA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>linkedin:4466513389</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-graduate-tech-and-product-usds-2027-start-at-tiktok-usds-joint-venture-4446630169?position=4&amp;pageNum=0&amp;refId=OabEITA2YNRn6ahbARU6dg%3D%3D&amp;trackingId=Ex2R5tWMtg3txyc%2Bzo9Yzg%3D%3D</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>linkedin:4446630169</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-workflow-specialist-graduate-at-hewlett-packard-enterprise-4467960534?position=9&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=UFlzjJkt8esqz8K7Ej2u6w%3D%3D</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>linkedin:4467960534</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6279f0846162391c9360fb</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Role is explicitly outside the US in Cape Town, South Africa. Location listed as 'Capetown', asks 'Are you eligible to live and work in South Africa', 'Are you willing to relocate to Cape Town at your own cost?', salary 'in ZAR', with no US location.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>url:a6c91cb3b26ca1383bd3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-entry-to-expert-level-maryland-at-national-security-agency-4467969614?position=6&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=H33trjRW8b%2F8tz0tIK61ng%3D%3D</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Job explicitly states 'U.S. Citizenship is required for all applicants.'</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>linkedin:4467969614</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/ai-engineer-entry-level-at-jobright-ai-4467100735?position=1&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=y818rXkZyP85j9yXFlXFqA%3D%3D</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>linkedin:4467100735</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/software-engineer-graduate-aml-engine-forge-platform-2027-start-at-bytedance-4467996442?position=3&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=z%2Fad2gEWCtx5eV8%2F6Gjupw%3D%3D</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>linkedin:4467996442</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-graduate-tech-and-product-usds-2027-start-at-tiktok-usds-joint-venture-4446614543?position=4&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=JJPnLx3dBj2eSNQKDeT9eA%3D%3D</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>linkedin:4446614543</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/machine-learning-engineer-applied-ai-%E2%80%94-new-grad-at-jobright-ai-4467115287?position=2&amp;pageNum=0&amp;refId=Fgk688949dn%2BoSguNhHTAg%3D%3D&amp;trackingId=qe%2FgUh%2B154sR4NekEiTLeg%3D%3D</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>linkedin:4467115287</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa9b06d09ae03adcacde5de</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Requires U.S. citizenship ('U.S. Citizen Only') and security clearance ('Security Clearance Required', 'Must have an active Secret clearance with ability to obtain TS/SCI with CI Poly').</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>url:affe0c806e18e42aeba6</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a724f9aee751e0c793483bd</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>url:c275b39f446272156d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaad1c840807b73bd3922fc</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>U.S. Citizen Only and Security Clearance Required: 'Must have an active Secret clearance with ability to obtain TS/SCI'</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>url:ca5eedb7c733f08776e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaab684c85610f4a48410a2</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>url:ee39c936ecb8f17a0521</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaaa04c40807b73bd390fb0</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Employer explicitly states: 'This role is not open to visa sponsorship or transfer of visa sponsorship including those on H1-B, F-1, OPT, STEM-OPT, or TN visa'</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>url:3ca3bd389e4d9f96d380</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a53ff39d007ee02d95fd55d</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>User requested to skip this application; not submitted. Observed blockers: active reCAPTCHA and LinkedIn-profile field enforcing phone-number validation.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>url:216037db555f09b90981</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a840e90e021cc586fb69474</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Page explicitly displays 'This job has closed.' indicating the role is closed and no longer accepting applications.</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>url:4947fe94fa4bb907b0fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aab91ab76707040fb085884</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Job page explicitly states 'This job has closed.' </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>url:c2f2b578ea90d7f97304</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aab772b4be87a72913a46e6</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>url:7474fb4e4bdc7fbd24ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa9ed7809ae03adcace043c</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>url:5661306cb37108ff0bba</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9a51851388387060593301</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>url:b6b07ca75967e428ef07</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9e29e175edfa11b47106c5</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>url:8672497a6a021b180077</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa1de0c0ffb3d4fea6b7891</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>url:6fea74027069a624da6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa48855422289703bd66f2a</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>url:2a07cfff8190d5b87d91</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/data/invalid_jobs.xlsx
+++ b/data/invalid_jobs.xlsx
@@ -453,11 +453,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
-    <col width="42.14285714285715" customWidth="1" min="1" max="1"/>
-    <col width="63.14285714285715" customWidth="1" min="2" max="2"/>
+    <col width="42.14285714285715" customWidth="1" min="1" max="2"/>
     <col width="24.42857142857143" customWidth="1" min="3" max="3"/>
     <col width="13.57142857142857" customWidth="1" min="4" max="24"/>
   </cols>
@@ -1220,7 +1219,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Employer explicitly states: 'This role is not open to visa sponsorship or transfer of visa sponsorship including those on H1-B, F-1, OPT, STEM-OPT, or TN visa'</t>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1327,6 +1326,11 @@
           <t>https://jobright.ai/jobs/info/6a9e29e175edfa11b47106c5</t>
         </is>
       </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>url:8672497a6a021b180077</t>
@@ -1351,10 +1355,1106 @@
           <t>https://jobright.ai/jobs/info/6aa48855422289703bd66f2a</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>url:2a07cfff8190d5b87d91</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a7cbbdf83621355407ab897</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>url:10a7749ff2ab8ad6ac55</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aab8c54f6bd9d2d17c1cb87</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>U.S. citizenship explicitly required: page shows 'U.S. Citizen Only' and 'Must have a Secret security clearance'</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>url:1f6f416e490389d5a7ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a05c8bc7c753c287f6fb895</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>url:0fa71f0191e382e249a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaac0a740807b73bd391b17</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>url:2adbf3b081ac480066db</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a95c0cdcabc9f6703e19976</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Job explicitly requires U.S. citizenship ('U.S. Citizen Only', 'Candidate must be a US Citizen') and security clearance ('Security Clearance Required', able to obtain DoD Secret Clearance).</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>url:02d54c7ed39bdf2b708e</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa9f4a26d0edc2d91b0cc13</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Page explicitly states 'This job has closed' and 'The job you clicked on is no longer available.'</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>url:f490955ea91413932cdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac99a03e3ce93970c7dfbe</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>url:31e1985462ef5050a398</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://smithfieldfoods.wd1.myworkdayjobs.com/en-US/Careers/job/Suffolk%2C-VA/Software-Engineer_R-2026-6268/apply/applyManually?jr_id=6a05c8bc7c753c287f6fb895</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>url:30745e3d0a2f4192a564</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4465986970/?companyName=BrothersTech&amp;trackingId=SPcfJwxkTxCEeWupAz4D8A%3D%3D&amp;applicantTrackingSystemName=LinkedIn</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>linkedin:4465986970</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6265a2c28982326de96827</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Employer explicitly excludes OPT: 'At this time, Wellmark is not considering applicants for this position that require any type of immigration sponsorship... This includes, but IS NOT LIMITED TO: F1-OPT, F1-CPT, H-1B, TN, L-1, J-1, etc'</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>url:6fd2e8501b35c58df442</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a871651e8b6601d12901934</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page explicitly states 'This job has closed' and 'The job you clicked on is no longer available.' </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>url:1ac465ff657cf390e2a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a73341832ebbc14ffb4d88a</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NO_EVIDENCE_OF_INELIGIBILITY</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>url:f4abea5a599c6744f952</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aabc3ef7007e606cc3d4fea</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>url:4efc8570108f842a2486</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a7239a745b6af1c30dbd688</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>url:19f23bfb58e5250aca56</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a98269383fc63335762fd55</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>url:87ae0db533a98a26137e</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aabfc1c3e3ce93970c7afcc</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>url:9dfe97584f744ddc6364</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://deluxe.wd5.myworkdayjobs.com/en-US/usa_can/job/New-York%2C-NY%2C-USA/Data-Scientist-1_260475WD-1/apply/applyManually?jr_id=6a73341832ebbc14ffb4d88a</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>url:15539e1ed650927b7d80</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://login.ibm.com/authsvc/mtfim/sps/authsvc?PolicyId=urn:ibm:security:authentication:asf:basicldapuser&amp;Target=https%3A%2F%2Flogin.ibm.com%2Foidc%2Fendpoint%2Fdefault%2Fauthorize%3Fclient_id%3DZmNmMjY5NjMtZTBlZS00%26stateId%3D0efadcde-017a-4e01-ac98-bb02b528eb08</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BLOCKED_BY_LOGIN</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>url:1c423081e1aee706ce84</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aacc17095c707f49dff22c2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>url:074a18443ad202d6e35e</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa8c09f3387a3d9b67d2fb2</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>url:50076cfb09d2fd77910f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac13823d96632d741a907d</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>url:118050780ab79f82e367</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac4a0e2e757fcb5c8b4c7a</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>url:9dc72c3bd64b4036dcda</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a95bc764c22023a079356e3</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>url:528e0106ff429d024a15</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac8b033d96632d741ab557</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>url:ffda0cbe6d1df9cb8f01</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac2f312e757fcb5c8b4396</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>url:bc428574898919f9c150</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a5fb44bf68dd368023e81c4</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>url:077e925e040ab80b68c2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aac35703dbb1f8967ce977e</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>url:7ac49ef0385d703b5ba0</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a52be098a74e077472f5cda</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>User confirmed already applied for this Brellium Software Engineer - AI role; skipping to avoid duplicate submission per user request.</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>url:540f3ced8634fe2b53cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aae4bce3d96632d741b0d09</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Application page states this is not a real job and for testing purposes only with no active job - 'This is not a real job. Do not submit this application' and 'There is not an active job for you to apply to. No one will respond.' Submitting would violate policy for fake/closed postings.</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>url:c922d479e63f17061e67</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aad8714de327d3e210d2fb1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>url:d98c4664ada7e47f4b4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aadce86de327d3e210d476a</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>User asked to skip to next job. Application not submitted; required Perplexity Exercise shared URL still missing.</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>url:f3c44a4ffaf4dd8e67b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/694363b194730b7398767863</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>url:5e2c849ad0dc3a99bd74</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a93639ec12c90443efcc07d</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>url:86da531dc568ae1a27e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aad247b3dbb1f8967cec19a</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>url:e3cb1be8a63f78ac4d5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6caccbacb0a61f9dbc6542</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>url:5355da1878c7be3ba391</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a3592da1232144fb1563d7a</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>url:ae88fa1f1794a7db8409</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaedb98de327d3e210d614e</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>User requested to skip this Infor application after CAPTCHA block on submission page.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>url:bb32e7eb57d6b8c5d577</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/69fa836081706a5bd2175ffa</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>url:1d498d4a23cc68c27cc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.dice.com/jobs?filters.postedDate=THREE&amp;q=entry+level+ai+engineer&amp;selectedJobId=be295c60-f104-468b-8e11-b9a9d2cfe7c0</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>User requested to skip this CNH application after resume upload control failed with no file input available.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>url:77d6a0a01571561f2701</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.dice.com/jobs?filters.postedDate=THREE&amp;q=entry+level+ai+engineer&amp;selectedJobId=28fd3571-d167-42d5-91a8-10dfa99b5539</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>url:86e4721adaec4e65d17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab0d23ddd960b415641a1a0</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>url:c517a85f2182f404a489</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaafaa676707040fb083662</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>url:0d2abdeaacb732bf1307</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab06125d3af3856cd992c53</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>url:136d31689aee6c332df5</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1938a32552369083e302f</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>url:679c5c5a3a2624c86921</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1464b32552369083e103c</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Infor application page states 'for internal candidates only' and rejects gmail with 'Email must be from an allowed internal email domain (e.g., infor.com)'. External applicant is ineligible for this internal-only flow.</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>url:24703fe2c4b0bc20459e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a0f822183d7144289821054</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Ashby blocked submission as duplicate/recent application: 'We couldn't submit your application. Since you've applied to one of our roles recently, we ask for some time before applying to other open positions.' No new application was submitted.</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>url:acb9cf4e8d7573010a83</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1a94ad2a93d5a97ebc25f</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>url:1921a1c1fc1cfa9cef63</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab193f6d43eb922ca0bfc22</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>url:db081bb2e1129e0b30da</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab153f0191d8c340dbd9de6</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>url:04b217e8ad9a9581e1c9</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.capitalonecareers.com/job/mclean/technology-development-program-associate-february-2027/31238/99973065696</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>url:a209af2328fb97cbf3cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab183ca23005eee3545ae0b</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>url:69e8e7e1c880769deee7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1a425f9692ca98b04ae7c</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>User asked to skip and move on; Step 6 tax survey requires SSN for complete/opt-out, unavailable, so application left incomplete and recorded as not applied.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>url:473fc9a43f981f417efa</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6b74b35c54bc4752ce9058</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>url:b6af65a24c3f0f2f73b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1684f32552369083e1eda</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>url:a6a86ab07d8302db8104</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1879e191d8c340dbdb376</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>url:f2a22f303cc344dc2767</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab16cccf9692ca98b0497ff</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>url:ac1991fa27bdc6581f0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1b3ded43eb922ca0c0c46</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>url:17a259bd809b985ca26c</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1d39e23005eee3545cb59</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>url:5b6a65c3c10db2d28240</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab18d25d2a93d5a97ebb548</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>url:7e277abf7b6021a50800</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab13b1bf9692ca98b0483c8</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>url:0a731d30ef1311f066ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a87694fe8b6601d129037d7</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>url:ba34ec13c46fa863d246</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab19783191d8c340dbdbab3</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>url:83faa79fe9917db71b6a</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a31e5440ff23769fdb20f07</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>url:a1b5bf39f1042e2f4cdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9e9ed22c964816f65edf4a</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>url:f224a7b55a0e026f09cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab2c4d230340229a322f9c5</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>url:f5092bdd5006e854fc2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab302711e4847ddae917cd5</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>url:23617f1748aa6551e3ec</t>
         </is>
       </c>
     </row>

--- a/data/invalid_jobs.xlsx
+++ b/data/invalid_jobs.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C121"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="42.14285714285715" customWidth="1" min="1" max="2"/>
@@ -2240,221 +2240,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://jobright.ai/jobs/info/6ab1684f32552369083e1eda</t>
+          <t>https://jobright.ai/jobs/info/6ab56a72d85922de20ce0eba</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Login failed</t>
+          <t>ALREADY_APPLIED</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>url:a6a86ab07d8302db8104</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab1879e191d8c340dbdb376</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>url:f2a22f303cc344dc2767</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab16cccf9692ca98b0497ff</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>url:ac1991fa27bdc6581f0a</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab1b3ded43eb922ca0c0c46</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>url:17a259bd809b985ca26c</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab1d39e23005eee3545cb59</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>NEEDS_SECURITY_CLERANCE</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>url:5b6a65c3c10db2d28240</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab18d25d2a93d5a97ebb548</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>url:7e277abf7b6021a50800</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab13b1bf9692ca98b0483c8</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>url:0a731d30ef1311f066ef</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6a87694fe8b6601d129037d7</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>url:ba34ec13c46fa863d246</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab19783191d8c340dbdbab3</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>url:83faa79fe9917db71b6a</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6a31e5440ff23769fdb20f07</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>url:a1b5bf39f1042e2f4cdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6a9e9ed22c964816f65edf4a</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>url:f224a7b55a0e026f09cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab2c4d230340229a322f9c5</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>url:f5092bdd5006e854fc2e</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>https://jobright.ai/jobs/info/6ab302711e4847ddae917cd5</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>US_CITIZENSHIP_REQUIRED</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>url:23617f1748aa6551e3ec</t>
+          <t>url:7837691e3a86b6e190b1</t>
         </is>
       </c>
     </row>

--- a/data/invalid_jobs.xlsx
+++ b/data/invalid_jobs.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="42.14285714285715" customWidth="1" min="1" max="2"/>
@@ -2254,6 +2254,1060 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a9af73bd5ff1f3f1c39caae</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>url:3025b0ba356efc6a731c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab9f93381e327c4bf206b59</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>JOB_CLOSED_OR_EXPIRED</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>url:2b1cc83c9d11dfdc1bfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abb2131be5f1e9325119bac</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>No qualifying Infosys confirmation email found; confirmation URL shows 404 NOT FOUND with no submission receipt, so application cannot be confirmed.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>url:366d03d96277b307128e</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a51db9978e364789ca5def0</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>url:14417aa131531e66f6b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abaa6c0d2914e9273eec802</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>url:4f4abb937cf90211fccd</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abbd093d6acfd3dd29fa089</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Submission blocked by hCaptcha verification failing with 'There was an error verifying your application. Please try again.' after resume re-attach as jaswanth_resume.pdf; user instructed to move on to next application.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>url:223e987e9d47eed79175</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abc47eed6acfd3dd29fd078</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Required cover letter blocks submission and no cover letter file was supplied; user instructed to skip this application and move to next.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>url:942968d6d9aaae9d233b</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abbbfb3d6acfd3dd29f9b30</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>url:8bb1ae41bf219bb4f567</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab67f20d85922de20ce5015</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>url:76eaf3c44808a7d91001</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abc032692b2612ef0f8c5c1</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>url:3de72666f3812990b1a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abb24f57220f52e62aeaac8</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>url:b21fc2380ab851044d36</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abbdc233217d1d13329b4a9</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>JOB_CLOSED_OR_EXPIRED</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>url:88a26234d3af7ef949c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abd5edb064da25272dfd346</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OPT_STEM_NOT_SUPPORTED</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>url:e9559edeb5511a67bd3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a8358882dbaf907b0768185</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>url:022f215a4a3b497262b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6abdc60d8ff3fb9b3bc720c2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Clearly ineligible: Applicant is not US Citizen/LPR (answered No, citizenship India, visa F-1 OPT) and selected F-1 + F-1 OPT work authorization. Job states individuals needing sponsorship now or future including F-1 OPT/CPT, H-1, J-1 are not eligible and no sponsorship provided, No H1B. Truthful sponsorship answer would be Yes.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>url:5390dfd9e27b71cb4bbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/69dfac04e34484770f1a9b5c</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>url:9f7df9f40f5506fa523a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/69c5554e83ea553769fc8cee</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Cannot truthfully complete required faith-based fields on Lever form (church attendance, 3x Christian/ministry I-agree affirmations, and salvation testimony). No supported answer in profile, resume, or saved answers; inferring would invent personal religious facts. Custom resume uploaded and supportable fields filled, but application left unsubmitted per fallback instruction.</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>url:ab4545cd2c1c89015a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a82f13b379c304e892f3f8f</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>NEEDS_SECURITY_CLERANCE</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>url:69f3557e8f895ccee582</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a467c7c971cd25b06f8ee69</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>url:1bd50fae2f7274b9a17c</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac02b50d9621c5b28396bb3</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>url:5aeb6bb60ba811d397d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac282a0372c01f6cd72f3d5</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>url:a5ef418315469763562d</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>http://jobright.ai/jobs/info/6ac2d67c064da25272e0d761</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>url:778603cf7b186f3103e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a89d597e8b6601d1290a40c</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>url:d050865ce9aae4362fdd</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa3b3ef626f9945308b2873</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>url:8cc3ee73b73236d77cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a6ccbe4ca1f933846600a31</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>url:4e986bd3abeb6558a76e</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aaaeb6f76707040fb08313e</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>url:823fd087e0af0a170339</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa3fe88c1928370a285befa</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Password and Re-type Password are required on the Epic Employment Inquiry form and no saved credential exists. Please set a compliant password directly on the page so the application can be submitted.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>url:bbcf806f22e4562d10c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac26d9ad9621c5b2839a102</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>JOB_CLOSED_OR_EXPIRED</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>url:bb55da05dc1a21880532</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac450788ff3fb9b3bc8540c</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Encountered a login issue: Authentication not completed. Email entered and terms accepted on JPMC Candidate Experience, but hCaptcha challenge (drag pipe) blocks proceeding past the email gate.. Would you like to complete sign-in manually, or continue with the next application?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>url:55e6f9ee4ad0f8f72d57</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac3e571372c01f6cd732bbd</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>NOT_APPLIED: Required LinkedIn field 'How many years of work experience do you have with React.js?' on 4/6 page has no truthful value in profile, resume, or saved answers, and duration cannot be inferred without inventing experience. Human timed out twice. Application was not submitted; dialog remains on Additional Questions.</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>url:edbfdccee1771c4081e5</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac46e26064da25272e12af3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Encountered a login issue: Entered email on iCIMS Enter Your Information screen for CubeSmart Req 26838, but hCaptcha image challenge blocked progress. Authentication not completed.. Would you like to complete sign-in manually, or continue with the next application?</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>url:dc3fcfcff194febbb5ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac3e3948ff3fb9b3bc82cd8</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>url:8a02598e8ea59a44e8e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab1263d32552369083e07a4</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Clearly ineligible and no truthful option: actual graduation May 2025 = Before September 2026 outside required Fall 2026-Summer 2027 window, and resume shows 0 internships while form only offers 1 or 2+ with no zero option. Cannot answer without inventing.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>url:e501433c9e80f35df19b</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac410ed064da25272e11081</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>NOT_APPLIED: Step 1 validation blocks Next Step - required Company Phone, Address, City, State, Zip for Zenith Technology and Accessifiers plus Reason for Leaving for Accessifiers. No company phones/addresses or reason for leaving in profile, resume, or saved answers; cannot invent. Custom resume jaswanth_resume.pdf was uploaded and personal/education fields filled, but submission not completed.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>url:12016a397c2d36eb5c41</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>https://lnkd.in/ddMhSCSS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>url:198834c7b7b143bd26ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>https://lnkd.in/dXyswnD5</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>url:2bc1db7527b61739a33a</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>https://lnkd.in/daDx8mXU</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>url:47b688b257a6f72bc588</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>https://lnkd.in/duTe53Je</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>url:3434bdaed7e0e6b93c4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acae7ff3c831dc4086bcb97</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>url:3b4b468262eb02cf9018</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acd50583c831dc4086c1b4e</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please complete the active reCAPTCHA image challenge (select all squares with buses) on the NAVEX application Submit page so submission can be completed.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>url:3d183b792a174090b4de</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acd12ac3c831dc4086c0636</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>ROLE_OUTSIDE_US</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>url:8a705e2c0bd8af415a4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acd4a44d113c967e3c7d286</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please solve the active hCaptcha challenge ('Click on things filled with air') on the application page to allow submission to complete.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>url:cb57caf5f60d0ca3f1d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aa3d3b43a768473c9369ab3</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>url:bbc30a4bd5dca0b74d5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acd00ec002e496d4beeffa8</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>US_CITIZENSHIP_REQUIRED</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>url:dd550c24605be16a96a7</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6aba228458caa3fb611b2137</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Required field Deutschkenntnisse (minimum C1 per job description) has no truthful value in profile, resume, or saved answers and cannot be reasonably inferred. Submitting with a guessed level would invent credentials. Application left unsubmitted with submit button disabled.</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>url:07912f5041f4dc44167c</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a3eb2444d047136e09374d3</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Job URL already exists in applied_jobs.xlsx</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>url:67baef259c82bd58eae6</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ab59151c6fe0dec811a21e5</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please solve the hCaptcha image challenge on the Laminar application page to allow submission to complete.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>url:7f34887797d64493f401</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acd5e98ddd23cce28a12214</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>url:bbe7652d3abc92794e20</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>https://www.dataannotation.tech/job-board/machine-learning-engineer?li_fat_id=948de0d5-bca9-4fac-ac9b-c2bc35850461&amp;viewingBehavior=NATIVE_WEBVIEW&amp;utm_campaign=1216794856&amp;worker_src=L&amp;utm_medium=display&amp;utm_content=1629699766&amp;utm_adgroup=907520706&amp;utm_source=linkedin&amp;projects=ML_ENG</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>url:ca917fc4763adebcb2a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>https://www.ziprecruiter.com/jobs-search?search=Entry-level+Ai+Engineer&amp;location=United+States&amp;location_explicitly_set=true&amp;radius=25&amp;days=1&amp;refine_by_employment=&amp;refine_by_location_type=&amp;refine_by_salary=&amp;refine_by_salary_ceil=&amp;refine_by_apply_type=&amp;refine_by_experience_level=&amp;seniority_filters_explicitly_set=&amp;apply_types_explicitly_set=&amp;employment_types_explicitly_set=&amp;location_types_explicitly_set=&amp;radius_explicitly_set=&amp;lk=dxhX-boRhlqnkW23qqKV2A</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>url:e6959d417fe7746570d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>https://www.ziprecruiter.com/jobs-search?search=Entry-level+Ai+Engineer&amp;location=United+States&amp;location_explicitly_set=true&amp;radius=25&amp;days=1&amp;refine_by_employment=&amp;refine_by_location_type=&amp;refine_by_salary=&amp;refine_by_salary_ceil=&amp;refine_by_apply_type=&amp;refine_by_experience_level=&amp;seniority_filters_explicitly_set=&amp;apply_types_explicitly_set=&amp;employment_types_explicitly_set=&amp;location_types_explicitly_set=&amp;radius_explicitly_set=&amp;lk=XlqH2LZfq_GyYlVq3Sia7Q</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>NOT_A_JOB_POSTING</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>url:a7d3eea4131736d7813c</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>https://careers.worldpac.com/careers-home/jobs/4762/job?utm_source=Monster_integration&amp;iis=Job%20Board&amp;iisn=Monster&amp;applyClickId=b30380cb-0527-404d-a3c6-ca044cd02816</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Login failed</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>url:6e0b4660001a04f79e7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acece204f3229123da3e22b</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>JOB_CLOSED_OR_EXPIRED</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>url:8acc02060e17f13af015</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ac5a6c64ac55253f5d77802</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>url:7ec7f980805960c6eaca</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ace77e8ba99f15ef4124e4f</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please complete the active hCaptcha challenge ('Please click on the TWO ends of the line') on the application page, then the agent can click Send to submit.</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>url:89e8611272258216b95d</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acdbbd409635d4ede00ac6f</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>url:e4e7e52aeffa0666bbaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6acde6c3ee9da536dc21b433</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>url:905b3a6f550d3871e13e</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6a55b7e614f1040fa611acea</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please attach the customized resume PDF (jaswanth_resume.pdf) to the required Resume upload field on this Auger application page, then confirm. I will complete verification and submit.</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>url:5c32494858489c9c6661</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ace903bbb78de94580d6f7e</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>url:5e9b7522590adab62e5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ace72334f3229123da3c084</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>url:e6c36dc39816e0012bfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ace76cbba99f15ef4124e07</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Human input timed out after 60 seconds; moving to next job. Please complete the 'Getting You Started' dialog (Legal First Name, Legal Last Name, Email, Confirm Email, Primary Phone, SMS consent) and click Continue To Application, then leave the application on the next step for automation to continue.</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>url:839882c4095c1b2ebf4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://jobright.ai/jobs/info/6ace420ca0453f9ba624794d</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>url:6b32c7b4038c88265c85</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
